--- a/测试.xlsx
+++ b/测试.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="34">
   <si>
     <t>日期</t>
   </si>
@@ -57,54 +57,33 @@
     <t>父亲去世</t>
   </si>
   <si>
-    <t>2025.07.16</t>
-  </si>
-  <si>
     <t>黄林轩</t>
   </si>
   <si>
     <t>母亲去世</t>
   </si>
   <si>
-    <t>2025.07.10</t>
-  </si>
-  <si>
     <t>李康军</t>
   </si>
   <si>
-    <t>2025.07.06</t>
-  </si>
-  <si>
     <t>孙少尘</t>
   </si>
   <si>
     <t>岳父去世</t>
   </si>
   <si>
-    <t>2025.06.24</t>
-  </si>
-  <si>
     <t>刘勇</t>
   </si>
   <si>
     <t>大伯去世</t>
   </si>
   <si>
-    <t>2025.06.22</t>
-  </si>
-  <si>
     <t>罗家兴</t>
   </si>
   <si>
-    <t>2025.06.21</t>
-  </si>
-  <si>
     <t>陈善维</t>
   </si>
   <si>
-    <t>2025.05.21</t>
-  </si>
-  <si>
     <t>尹绍汉</t>
   </si>
   <si>
@@ -114,18 +93,12 @@
     <t>失火</t>
   </si>
   <si>
-    <t>2025.05.02</t>
-  </si>
-  <si>
     <t>刘国</t>
   </si>
   <si>
     <t>前三审去世</t>
   </si>
   <si>
-    <t>2025.05.01</t>
-  </si>
-  <si>
     <t>陈善美</t>
   </si>
   <si>
@@ -138,25 +111,10 @@
     <t>郑昌和</t>
   </si>
   <si>
-    <t>2025.04.24</t>
-  </si>
-  <si>
     <t>尹钊</t>
   </si>
   <si>
     <t>大叔去世</t>
-  </si>
-  <si>
-    <t>2025.07.21</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025.09.19</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025.09.21</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>覃正龙</t>
@@ -228,9 +186,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -538,7 +500,7 @@
   <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="12.9" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="4" max="4" width="19.5" customWidth="1"/>
+    <col min="4" max="4" width="19.5" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.15">
@@ -551,7 +513,7 @@
       <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
@@ -571,8 +533,8 @@
       <c r="C2">
         <v>500</v>
       </c>
-      <c r="D2" t="s">
-        <v>44</v>
+      <c r="D2" s="2">
+        <v>45921</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -586,19 +548,19 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="C3">
         <v>500</v>
       </c>
-      <c r="D3" t="s">
-        <v>43</v>
+      <c r="D3" s="2">
+        <v>45919</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.15">
@@ -611,8 +573,8 @@
       <c r="C4">
         <v>2500</v>
       </c>
-      <c r="D4" t="s">
-        <v>42</v>
+      <c r="D4" s="2">
+        <v>45859</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -626,19 +588,19 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C5">
         <v>500</v>
       </c>
-      <c r="D5" t="s">
-        <v>12</v>
+      <c r="D5" s="2">
+        <v>45854</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.15">
@@ -646,13 +608,13 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C6">
         <v>500</v>
       </c>
-      <c r="D6" t="s">
-        <v>15</v>
+      <c r="D6" s="2">
+        <v>45848</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -663,19 +625,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C7">
         <v>500</v>
       </c>
-      <c r="D7" t="s">
-        <v>17</v>
+      <c r="D7" s="2">
+        <v>45844</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.15">
@@ -683,19 +645,19 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C8">
         <v>5000</v>
       </c>
-      <c r="D8" t="s">
-        <v>20</v>
+      <c r="D8" s="2">
+        <v>45832</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.15">
@@ -703,13 +665,13 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C9">
         <v>500</v>
       </c>
-      <c r="D9" t="s">
-        <v>23</v>
+      <c r="D9" s="2">
+        <v>45830</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -723,19 +685,19 @@
         <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C10">
         <v>500</v>
       </c>
-      <c r="D10" t="s">
-        <v>25</v>
+      <c r="D10" s="2">
+        <v>45829</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.15">
@@ -743,19 +705,19 @@
         <v>6</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C11">
         <v>400</v>
       </c>
-      <c r="D11" t="s">
-        <v>27</v>
+      <c r="D11" s="2">
+        <v>45798</v>
       </c>
       <c r="E11" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="F11" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.15">
@@ -763,19 +725,19 @@
         <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C12">
         <v>500</v>
       </c>
-      <c r="D12" t="s">
-        <v>31</v>
+      <c r="D12" s="2">
+        <v>45779</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.15">
@@ -783,16 +745,16 @@
         <v>6</v>
       </c>
       <c r="B13" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="C13">
         <v>300</v>
       </c>
-      <c r="D13" t="s">
-        <v>34</v>
+      <c r="D13" s="2">
+        <v>45778</v>
       </c>
       <c r="E13" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.15">
@@ -800,16 +762,16 @@
         <v>6</v>
       </c>
       <c r="B14" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="C14">
         <v>500</v>
       </c>
-      <c r="D14" t="s">
-        <v>34</v>
+      <c r="D14" s="2">
+        <v>45778</v>
       </c>
       <c r="E14" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.15">
@@ -817,13 +779,13 @@
         <v>6</v>
       </c>
       <c r="B15" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="C15">
         <v>4000</v>
       </c>
-      <c r="D15" t="s">
-        <v>34</v>
+      <c r="D15" s="2">
+        <v>45778</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -837,19 +799,19 @@
         <v>6</v>
       </c>
       <c r="B16" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C16">
         <v>1000</v>
       </c>
-      <c r="D16" t="s">
-        <v>39</v>
+      <c r="D16" s="2">
+        <v>45771</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
